--- a/data_traduction.xlsx
+++ b/data_traduction.xlsx
@@ -31742,34 +31742,34 @@
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
+          <t>Nouvelle version</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>Nouvelle version</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>Nouvelle version</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Nouvelle version</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>Ancienne version</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
           <t>Non traduit</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>Non traduit</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Non traduit</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>Non traduit</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>Ancienne version</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="inlineStr">
-        <is>
-          <t>Non traduit</t>
-        </is>
-      </c>
       <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Non enregistré</t>
@@ -31805,10 +31805,26 @@
           <t>copain annette</t>
         </is>
       </c>
-      <c r="U15" s="10" t="n"/>
-      <c r="V15" s="10" t="n"/>
-      <c r="W15" s="10" t="n"/>
-      <c r="X15" s="10" t="n"/>
+      <c r="U15" s="10" t="inlineStr">
+        <is>
+          <t>გაქვთ გასაუბრება OFPRA-ში?</t>
+        </is>
+      </c>
+      <c r="V15" s="10" t="inlineStr">
+        <is>
+          <t>ვინმეს ახლავხართ თან?</t>
+        </is>
+      </c>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>გნებავთ ჩაი, ყავა ან წყალი?</t>
+        </is>
+      </c>
+      <c r="X15" s="10" t="inlineStr">
+        <is>
+          <t>პარიზის რეგიონში ცხოვრობთ?</t>
+        </is>
+      </c>
       <c r="Y15" s="10" t="inlineStr">
         <is>
           <t>OASIS — ეს არის წითელი ჯვრის განყოფილება, რომელიც აქედან მხოლოდ 5 წუთის სავალზე მდებარეობს და სრულიად უფასოა. თქვენ შეგიძლიათ შიგნით, კომფორტულ გარემოში დაელოდოთ. აქ შესაძლებელია დასვენება, ტუალეტითა და აბაზანით სარგებლობა, ჩაის ან ყავის დალევა, ლოცვა ან სხვადასხვა აქტივობით დროის გაყვანა. ჩვენი გუნდი მზად არის თქვენს მისაღებად: ფსიქოლოგი, ანიმატორი და მოხალისეები. გაინტერესებთ ეს?</t>
@@ -32057,12 +32073,12 @@
       </c>
       <c r="Y17" s="10" t="inlineStr">
         <is>
-          <t>ה-OASIS הוא מסגרת של הצלב האדום, הנמצאת במרחק חמש דקות הליכה מכאן, וכל השירותים בה ניתנים בחינם לחלוטין. את יכולה לחכות בפנים, במקום נעים ונוח. את יכולה לנוח, להשתמש בשירותים ובמקלחת, לשתות תה או קפה, להתפלל, או להירגע קצת עם משחקי קופסה. את יכולה גם לטעון את הטלפון, להתחבר לרשת הוויפי ולהדפיס מסמכים. צוות שלם מחכה לקבל את פנייך: פסיכולוגית, מנחה ומתנדבות. האם זה מעניין אותך?</t>
+          <t>ה-OASIS הוא מסגרת של הצלב האדום, הנמצאת במרחק חמש דקות הליכה מכאן, וכל השירותים בה ניתנים בחינם לחלוטין. את/ה יכול/ה לחכות בפנים, במקום נעים ונוח. את/ה יכול/ה לנוח, להשתמש בשירותים ובמקלחת, לשתות תה או קפה, להתפלל, או להירגע קצת עם משחקי קופסה. את/ה יכול/ה גם לטעון את הטלפון, להתחבר לרשת הוויפי ולהדפיס מסמכים. צוות שלם מחכה לקבל אותך: פסיכולוגית, מנחה ומתנדבות. האם זה מעניין אותך?</t>
         </is>
       </c>
       <c r="Z17" s="10" t="inlineStr">
         <is>
-          <t>שלום, אני פסיכולוגית. אני מציעה פגישת ייעוץ אישית וללא תשלום. הפגישה הזו אנונימית וחסויה. אני יכולה לעזור לך להתמודד עם לחץ אם את סובלת ממנו, או לעזור לך למצוא ליווי פסיכולוגי קרוב לביתך אם זה מעניין אותך. פסיכולוג הוא אדם שמעניק עזרה וכלים להתמודדות עם קשיים יומיומיים הקשורים לשינה, לרגשות, לתיאבון ולכל דבר שיכול להשפיע על המצב הנפשי. האם היית מעוניינת בשיחה איתי?</t>
+          <t>שלום, אני פסיכולוגית. אני מציעה פגישת ייעוץ אישית וללא תשלום. הפגישה הזו אנונימית וחסויה. אני יכולה לעזור לך להתמודד עם לחץ אם את/ה סובל/ת ממנו, או לעזור לך למצוא ליווי פסיכולוגי קרוב לביתך אם זה מעניין אותך. פסיכולוג הוא אדם שמעניק עזרה וכלים להתמודדות עם קשיים יומיומיים הקשורים לשינה, לרגשות, לתיאבון ולכל דבר שיכול להשפיע על המצב הנפשי. האם היית מעוניין/ת בשיחה איתי?</t>
         </is>
       </c>
       <c r="AA17" s="10" t="inlineStr">

--- a/data_traduction.xlsx
+++ b/data_traduction.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Calculé tout seul, ne rien y écrire : le compte des 12 cases de la langue (6 traductions + 6 enregistrements), affiché « 9/12 ». Une « Ancienne version » vaut une demie, d'où les « 4,5/12 ». La barre de couleur remplit la cellule à proportion, pour voir l'avancement sans lire les chiffres.</t>
+          <t>Calculé tout seul, ne rien y écrire : le compte des 12 cases de la langue (6 traductions + 6 enregistrements), affiché « 9/12 ». Une « Ancienne version » vaut une demie, d'où les « 4,5/12 ». La cellule se teinte de l'orange au vert selon l'avancement, pour lire la colonne sans lire les chiffres.</t>
         </is>
       </c>
       <c r="C13" s="8" t="n"/>
@@ -50756,12 +50756,15 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G43">
-    <cfRule type="dataBar" priority="14">
-      <dataBar showValue="1">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
         <cfvo type="num" val="0"/>
+        <cfvo type="num" val="6"/>
         <cfvo type="num" val="12"/>
-        <color rgb="FF9DA679"/>
-      </dataBar>
+        <color rgb="FFF4BB8F"/>
+        <color rgb="FFF9EFA8"/>
+        <color rgb="FFC4C9AE"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">

--- a/data_traduction.xlsx
+++ b/data_traduction.xlsx
@@ -20,9 +20,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.#&quot;/12&quot;"/>
-    <numFmt numFmtId="165" formatCode="General&quot;/12&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General&quot;/12&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -33,23 +32,27 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="8"/>
     </font>
@@ -138,7 +141,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -31747,7 +31750,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>copain annette</t>
+          <t>copain annette/amie Eulalie</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -31782,34 +31785,34 @@
       </c>
       <c r="O15" s="7" t="inlineStr">
         <is>
+          <t>Enregistré</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>Enregistré</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>Enregistré</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr">
+        <is>
+          <t>Enregistré</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
           <t>Non enregistré</t>
         </is>
       </c>
-      <c r="P15" s="7" t="inlineStr">
+      <c r="T15" s="7" t="inlineStr">
         <is>
           <t>Non enregistré</t>
         </is>
       </c>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>Non enregistré</t>
-        </is>
-      </c>
-      <c r="R15" s="7" t="inlineStr">
-        <is>
-          <t>Non enregistré</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>Non enregistré</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>Non enregistré</t>
-        </is>
-      </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
           <t>გაქვთ გასაუბრება OFPRA-ში?</t>
@@ -31836,10 +31839,26 @@
         </is>
       </c>
       <c r="Z15" s="8" t="n"/>
-      <c r="AA15" s="8" t="n"/>
-      <c r="AB15" s="8" t="n"/>
-      <c r="AC15" s="8" t="n"/>
-      <c r="AD15" s="8" t="n"/>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>audio/ka_p1.mp3</t>
+        </is>
+      </c>
+      <c r="AB15" s="8" t="inlineStr">
+        <is>
+          <t>audio/ka_p2.mp3</t>
+        </is>
+      </c>
+      <c r="AC15" s="8" t="inlineStr">
+        <is>
+          <t>audio/ka_p3.mp3</t>
+        </is>
+      </c>
+      <c r="AD15" s="8" t="inlineStr">
+        <is>
+          <t>audio/ka_p4.mp3</t>
+        </is>
+      </c>
       <c r="AE15" s="8" t="n"/>
       <c r="AF15" s="8" t="n"/>
     </row>
@@ -32293,7 +32312,11 @@
         <f>COUNTIF(I19:N19,"Nouvelle version")+COUNTIF(O19:T19,"Enregistré")+0.5*(COUNTIF(I19:N19,"Ancienne version")+COUNTIF(O19:T19,"Ancienne version"))</f>
         <v/>
       </c>
-      <c r="H19" s="8" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Contact Eulalie (Tabita)</t>
+        </is>
+      </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
           <t>Non traduit</t>
@@ -32931,7 +32954,11 @@
         <f>COUNTIF(I24:N24,"Nouvelle version")+COUNTIF(O24:T24,"Enregistré")+0.5*(COUNTIF(I24:N24,"Ancienne version")+COUNTIF(O24:T24,"Ancienne version"))</f>
         <v/>
       </c>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Contact Eulalie</t>
+        </is>
+      </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
           <t>Non traduit</t>
@@ -33294,11 +33321,7 @@
         <f>COUNTIF(I27:N27,"Nouvelle version")+COUNTIF(O27:T27,"Enregistré")+0.5*(COUNTIF(I27:N27,"Ancienne version")+COUNTIF(O27:T27,"Ancienne version"))</f>
         <v/>
       </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Amie Eulalie (Vrinda)</t>
-        </is>
-      </c>
+      <c r="H27" s="8" t="n"/>
       <c r="I27" s="7" t="inlineStr">
         <is>
           <t>Non traduit</t>
@@ -35184,80 +35207,124 @@
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Non traduit</t>
+          <t>Nouvelle version</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>Non traduit</t>
+          <t>Nouvelle version</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>Non traduit</t>
+          <t>Nouvelle version</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>Non traduit</t>
+          <t>Nouvelle version</t>
         </is>
       </c>
       <c r="M42" s="7" t="inlineStr">
         <is>
-          <t>Ancienne version</t>
+          <t>Nouvelle version</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>Non traduit</t>
+          <t>Nouvelle version</t>
         </is>
       </c>
       <c r="O42" s="7" t="inlineStr">
         <is>
-          <t>Non enregistré</t>
+          <t>Enregistré</t>
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>Non enregistré</t>
+          <t>Enregistré</t>
         </is>
       </c>
       <c r="Q42" s="7" t="inlineStr">
         <is>
-          <t>Non enregistré</t>
+          <t>Enregistré</t>
         </is>
       </c>
       <c r="R42" s="7" t="inlineStr">
         <is>
-          <t>Non enregistré</t>
+          <t>Enregistré</t>
         </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>Non enregistré</t>
+          <t>Enregistré</t>
         </is>
       </c>
       <c r="T42" s="7" t="inlineStr">
         <is>
-          <t>Non enregistré</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="n"/>
-      <c r="V42" s="8" t="n"/>
-      <c r="W42" s="8" t="n"/>
-      <c r="X42" s="8" t="n"/>
+          <t>Enregistré</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>Чи маєте ви співбесіду в OFPRA?</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>Чи ви супроводжуєте когось?</t>
+        </is>
+      </c>
+      <c r="W42" s="8" t="inlineStr">
+        <is>
+          <t>Хочете чаю? Кави? Води?</t>
+        </is>
+      </c>
+      <c r="X42" s="8" t="inlineStr">
+        <is>
+          <t>Чи ви живете в Паризькому регіоні?</t>
+        </is>
+      </c>
       <c r="Y42" s="8" t="inlineStr">
         <is>
-          <t>OASIS — це структура Червоного Хреста, розташована всього за 5 хвилин пішки звідси, і повністю безкоштовна. Ви можете зачекати всередині у зручному місці. Тут можна відпочити, скористатися туалетом, ванною, випити чай або каву, помолитися або розважитися завдяки різним активностям. Наша команда готова вас прийняти: психолог, аніматор та волонтери. Вас це цікавить?</t>
-        </is>
-      </c>
-      <c r="Z42" s="8" t="n"/>
-      <c r="AA42" s="8" t="n"/>
-      <c r="AB42" s="8" t="n"/>
-      <c r="AC42" s="8" t="n"/>
-      <c r="AD42" s="8" t="n"/>
-      <c r="AE42" s="8" t="n"/>
-      <c r="AF42" s="8" t="n"/>
+          <t>OASIS — це безкоштовний центр Червоного Хреста, розташований за 5 хвилин ходьби звідси. Ви можете почекати всередині, у комфортному місці. Там ви зможете відпочити, скористатися туалетом і ванною кімнатою, випити чаю або кави, помолитися або відволіктися, граючи в настільні ігри. Ви також можете зарядити телефон, підключитися до Wi-Fi та роздрукувати документи. Ми — команда, яка рада вас вітати та підтримати: психолог, організатор активностей і волонтери. Чи були б ви зацікавлені?</t>
+        </is>
+      </c>
+      <c r="Z42" s="8" t="inlineStr">
+        <is>
+          <t>Доброго дня, я психолог. Я пропоную безкоштовну індивідуальну консультацію. Ця консультація є анонімною та конфіденційною. Я можу допомогти вам справлятися зі стресом, якщо ви з ним стикаєтеся, або, якщо хочете, допомогти знайти психологічну підтримку поблизу вашого місця проживання. Психолог — це людина, яка підтримує та надає інструменти для подолання повсякденних труднощів, пов’язаних зі сном, емоціями, апетитом та всім, що може впливати на психологічний стан. Чи хотіли б ви поговорити зі мною?</t>
+        </is>
+      </c>
+      <c r="AA42" s="8" t="inlineStr">
+        <is>
+          <t>audio/uk_p1.mp3</t>
+        </is>
+      </c>
+      <c r="AB42" s="8" t="inlineStr">
+        <is>
+          <t>audio/uk_p2.mp3</t>
+        </is>
+      </c>
+      <c r="AC42" s="8" t="inlineStr">
+        <is>
+          <t>audio/uk_p3.mp3</t>
+        </is>
+      </c>
+      <c r="AD42" s="8" t="inlineStr">
+        <is>
+          <t>audio/uk_p4.mp3</t>
+        </is>
+      </c>
+      <c r="AE42" s="8" t="inlineStr">
+        <is>
+          <t>audio/uk_p5.mp3</t>
+        </is>
+      </c>
+      <c r="AF42" s="8" t="inlineStr">
+        <is>
+          <t>audio/uk_p6.mp3</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="14.25" customHeight="1" s="11">
       <c r="A43" s="8" t="inlineStr">
